--- a/APS-Modules/aps-mp/src/main/resources/excelModel/salesOrderPool.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/salesOrderPool.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
-    <t>{title} 销售订单池明细</t>
+    <t>{yearAndMonth} 销售订单池明细</t>
   </si>
   <si>
     <t>合计</t>
@@ -185,8 +185,9 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -339,7 +340,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -348,14 +349,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="0"/>
         <bgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor rgb="FF00B050"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF008080"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -690,7 +697,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -714,16 +721,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -732,89 +739,89 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -823,11 +830,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1222,144 +1230,146 @@
       <c r="S1" s="2"/>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:19">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4">
+      <c r="N2" s="5">
         <f>SUM(N5:N995)</f>
         <v>0</v>
       </c>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:19">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="Q3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="R3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="S3" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:19">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="Q4" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="R4" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="S4" s="7" t="s">
         <v>39</v>
       </c>
     </row>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/salesOrderPool.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/salesOrderPool.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27950" windowHeight="12550"/>
+    <workbookView windowWidth="18350" windowHeight="7140"/>
   </bookViews>
   <sheets>
     <sheet name="销售订单池" sheetId="1" r:id="rId1"/>
@@ -169,17 +169,17 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -826,12 +826,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
